--- a/data/gravel/8Bar Mitte V1 Carbon 2in 1 2025.xlsx
+++ b/data/gravel/8Bar Mitte V1 Carbon 2in 1 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E6DDFA2-C074-9346-84E0-749A723F3B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5D224F-10D4-8047-921E-87DF7BEB2D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3080" yWindow="740" windowWidth="25400" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="37140" yWindow="-23540" windowWidth="25400" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -869,9 +869,22 @@
       <c r="F10" s="6">
         <v>576</v>
       </c>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
+      <c r="H10">
+        <f>C17 + C18/TAN(C14*PI()/180)</f>
+        <v>537.95445321746593</v>
+      </c>
+      <c r="I10">
+        <f t="shared" ref="I10:K10" si="0">D17 + D18/TAN(D14*PI()/180)</f>
+        <v>552.54041343934591</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="0"/>
+        <v>567.73783502414312</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="0"/>
+        <v>585.38110206060969</v>
+      </c>
       <c r="L10" s="6"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
